--- a/ข้อมูลครุภัณฑ์/รายงานรายการครุภัณฑ์คงทนที่ยังไม่มีรูปภาพ.updated.xlsx
+++ b/ข้อมูลครุภัณฑ์/รายงานรายการครุภัณฑ์คงทนที่ยังไม่มีรูปภาพ.updated.xlsx
@@ -1068,13 +1068,13 @@
         <v>11</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F29">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G29" t="str">
-        <v>45.5%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="30">
@@ -1114,13 +1114,13 @@
         <v>373</v>
       </c>
       <c r="E31">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F31">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G31" t="str">
-        <v>40.2%</v>
+        <v>41.8%</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M52"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -3204,31 +3204,31 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C51" t="str">
-        <v>EQ-NG-0001</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="D51" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="E51" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="F51" t="str">
-        <v>LF01174</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="G51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H51">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I51" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J51" t="str">
-        <v>1-B9701-FA17-65450010004/012-68 ถึง 1-B9701-FA17-65450010004/016-68 (มี 5 เลข)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (42-1/1) ถึง 1-B9701-FN17-65450010002/003-68 (มี 4 เลข)</v>
       </c>
       <c r="K51" t="str">
         <v>-</v>
@@ -3245,134 +3245,52 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C52" t="str">
-        <v>EQ-NG-0011</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="D52" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหารทางจมูก</v>
+        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E52" t="str">
         <v>Upright Simulation</v>
       </c>
       <c r="F52" t="str">
-        <v>หุ่น ครุภัณฑ์และอุปกรณ์ในห้องปฏิบัติการพยาบาลการเรียนรู้แบบเสมือนจริง</v>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="G52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I52" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J52" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (8-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (43-1/2) ถึง 2-B9701-FA17-65450010002/001-67 (43-2/2) (มี 2 เลข)</v>
       </c>
       <c r="K52" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="L52" t="str">
         <v/>
       </c>
       <c r="M52" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C53" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="D53" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="E53" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="F53" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="G53">
-        <v>4</v>
-      </c>
-      <c r="H53">
-        <v>4</v>
-      </c>
-      <c r="I53" t="str">
-        <v>ยังไม่มีรูปภาพเลย (0%)</v>
-      </c>
-      <c r="J53" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (42-1/1) ถึง 1-B9701-FN17-65450010002/003-68 (มี 4 เลข)</v>
-      </c>
-      <c r="K53" t="str">
-        <v>-</v>
-      </c>
-      <c r="L53" t="str">
-        <v/>
-      </c>
-      <c r="M53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C54" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="D54" t="str">
-        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="E54" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="F54" t="str">
-        <v>Patient Transfer Slide</v>
-      </c>
-      <c r="G54">
-        <v>2</v>
-      </c>
-      <c r="H54">
-        <v>2</v>
-      </c>
-      <c r="I54" t="str">
-        <v>ยังไม่มีรูปภาพเลย (0%)</v>
-      </c>
-      <c r="J54" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (43-1/2) ถึง 2-B9701-FA17-65450010002/001-67 (43-2/2) (มี 2 เลข)</v>
-      </c>
-      <c r="K54" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="L54" t="str">
-        <v/>
-      </c>
-      <c r="M54" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M54"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M52"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O224"/>
+  <dimension ref="A1:O218"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -13360,31 +13278,31 @@
         <v>212</v>
       </c>
       <c r="B213" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C213" t="str">
-        <v>EQ-NG-0001</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="D213" t="str">
-        <v>1-B9701-FA17-65450010004/012-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
       </c>
       <c r="E213" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F213">
         <v>1</v>
       </c>
       <c r="G213" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H213" t="str">
-        <v>LF01174</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I213" t="str">
         <v>-</v>
       </c>
       <c r="J213" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K213" t="str">
         <v>พร้อมใช้งาน</v>
@@ -13393,10 +13311,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M213">
-        <v>90000</v>
+        <v>7000</v>
       </c>
       <c r="N213" t="str">
-        <v>EQ-NG-0001</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O213" t="str">
         <v/>
@@ -13407,31 +13325,31 @@
         <v>213</v>
       </c>
       <c r="B214" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C214" t="str">
-        <v>EQ-NG-0002</v>
+        <v>EQ-TRS-0002</v>
       </c>
       <c r="D214" t="str">
-        <v>1-B9701-FA17-65450010004/013-68</v>
+        <v>1-B9701-FN17-65450010002/001-68</v>
       </c>
       <c r="E214" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F214">
         <v>2</v>
       </c>
       <c r="G214" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H214" t="str">
-        <v>LF01174</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I214" t="str">
         <v>-</v>
       </c>
       <c r="J214" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K214" t="str">
         <v>พร้อมใช้งาน</v>
@@ -13440,10 +13358,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M214">
-        <v>90000</v>
+        <v>1000</v>
       </c>
       <c r="N214" t="str">
-        <v>EQ-NG-0001</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O214" t="str">
         <v/>
@@ -13454,31 +13372,31 @@
         <v>214</v>
       </c>
       <c r="B215" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C215" t="str">
-        <v>EQ-NG-0003</v>
+        <v>EQ-TRS-0003</v>
       </c>
       <c r="D215" t="str">
-        <v>1-B9701-FA17-65450010004/014-68</v>
+        <v>1-B9701-FN17-65450010002/002-68</v>
       </c>
       <c r="E215" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F215">
         <v>3</v>
       </c>
       <c r="G215" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H215" t="str">
-        <v>LF01174</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I215" t="str">
         <v>-</v>
       </c>
       <c r="J215" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K215" t="str">
         <v>พร้อมใช้งาน</v>
@@ -13487,10 +13405,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M215">
-        <v>90000</v>
+        <v>1000</v>
       </c>
       <c r="N215" t="str">
-        <v>EQ-NG-0001</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O215" t="str">
         <v/>
@@ -13501,31 +13419,31 @@
         <v>215</v>
       </c>
       <c r="B216" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C216" t="str">
-        <v>EQ-NG-0004</v>
+        <v>EQ-TRS-0004</v>
       </c>
       <c r="D216" t="str">
-        <v>1-B9701-FA17-65450010004/015-68</v>
+        <v>1-B9701-FN17-65450010002/003-68</v>
       </c>
       <c r="E216" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F216">
         <v>4</v>
       </c>
       <c r="G216" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H216" t="str">
-        <v>LF01174</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I216" t="str">
         <v>-</v>
       </c>
       <c r="J216" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K216" t="str">
         <v>พร้อมใช้งาน</v>
@@ -13534,10 +13452,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M216">
-        <v>90000</v>
+        <v>1000</v>
       </c>
       <c r="N216" t="str">
-        <v>EQ-NG-0001</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O216" t="str">
         <v/>
@@ -13548,31 +13466,31 @@
         <v>216</v>
       </c>
       <c r="B217" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C217" t="str">
-        <v>EQ-NG-0005</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="D217" t="str">
-        <v>1-B9701-FA17-65450010004/016-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (43-1/2)</v>
       </c>
       <c r="E217" t="str">
-        <v>หุ่นฝึกการใส่สายให้อาหาร</v>
+        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="F217">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G217" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H217" t="str">
-        <v>LF01174</v>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="I217" t="str">
         <v>-</v>
       </c>
       <c r="J217" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K217" t="str">
         <v>พร้อมใช้งาน</v>
@@ -13581,10 +13499,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M217">
-        <v>90000</v>
+        <v>8000</v>
       </c>
       <c r="N217" t="str">
-        <v>EQ-NG-0001</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="O217" t="str">
         <v/>
@@ -13595,31 +13513,31 @@
         <v>217</v>
       </c>
       <c r="B218" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหาร</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C218" t="str">
-        <v>EQ-NG-0011</v>
+        <v>EQ-TRS-0006</v>
       </c>
       <c r="D218" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (8-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (43-2/2)</v>
       </c>
       <c r="E218" t="str">
-        <v>หุ่นฝึกใส่สายให้อาหารทางจมูก</v>
+        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="F218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G218" t="str">
         <v>Upright Simulation</v>
       </c>
       <c r="H218" t="str">
-        <v>หุ่น ครุภัณฑ์และอุปกรณ์ในห้องปฏิบัติการพยาบาลการเรียนรู้แบบเสมือนจริง</v>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="I218" t="str">
         <v>-</v>
       </c>
       <c r="J218" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K218" t="str">
         <v>พร้อมใช้งาน</v>
@@ -13628,300 +13546,18 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M218">
-        <v>60000</v>
+        <v>8000</v>
       </c>
       <c r="N218" t="str">
-        <v>EQ-NG-0011</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="O218" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219">
-        <v>218</v>
-      </c>
-      <c r="B219" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C219" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="D219" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
-      </c>
-      <c r="E219" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F219">
-        <v>1</v>
-      </c>
-      <c r="G219" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H219" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I219" t="str">
-        <v>-</v>
-      </c>
-      <c r="J219" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K219" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L219" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M219">
-        <v>7000</v>
-      </c>
-      <c r="N219" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O219" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220">
-        <v>219</v>
-      </c>
-      <c r="B220" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C220" t="str">
-        <v>EQ-TRS-0002</v>
-      </c>
-      <c r="D220" t="str">
-        <v>1-B9701-FN17-65450010002/001-68</v>
-      </c>
-      <c r="E220" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F220">
-        <v>2</v>
-      </c>
-      <c r="G220" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H220" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I220" t="str">
-        <v>-</v>
-      </c>
-      <c r="J220" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K220" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L220" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M220">
-        <v>1000</v>
-      </c>
-      <c r="N220" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O220" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221">
-        <v>220</v>
-      </c>
-      <c r="B221" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C221" t="str">
-        <v>EQ-TRS-0003</v>
-      </c>
-      <c r="D221" t="str">
-        <v>1-B9701-FN17-65450010002/002-68</v>
-      </c>
-      <c r="E221" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F221">
-        <v>3</v>
-      </c>
-      <c r="G221" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H221" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I221" t="str">
-        <v>-</v>
-      </c>
-      <c r="J221" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K221" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L221" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M221">
-        <v>1000</v>
-      </c>
-      <c r="N221" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O221" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222">
-        <v>221</v>
-      </c>
-      <c r="B222" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C222" t="str">
-        <v>EQ-TRS-0004</v>
-      </c>
-      <c r="D222" t="str">
-        <v>1-B9701-FN17-65450010002/003-68</v>
-      </c>
-      <c r="E222" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F222">
-        <v>4</v>
-      </c>
-      <c r="G222" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H222" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I222" t="str">
-        <v>-</v>
-      </c>
-      <c r="J222" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K222" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L222" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M222">
-        <v>1000</v>
-      </c>
-      <c r="N222" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O222" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223">
-        <v>222</v>
-      </c>
-      <c r="B223" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C223" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="D223" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (43-1/2)</v>
-      </c>
-      <c r="E223" t="str">
-        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="F223">
-        <v>1</v>
-      </c>
-      <c r="G223" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H223" t="str">
-        <v>Patient Transfer Slide</v>
-      </c>
-      <c r="I223" t="str">
-        <v>-</v>
-      </c>
-      <c r="J223" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K223" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L223" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M223">
-        <v>8000</v>
-      </c>
-      <c r="N223" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="O223" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224">
-        <v>223</v>
-      </c>
-      <c r="B224" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C224" t="str">
-        <v>EQ-TRS-0006</v>
-      </c>
-      <c r="D224" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (43-2/2)</v>
-      </c>
-      <c r="E224" t="str">
-        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="F224">
-        <v>2</v>
-      </c>
-      <c r="G224" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H224" t="str">
-        <v>Patient Transfer Slide</v>
-      </c>
-      <c r="I224" t="str">
-        <v>-</v>
-      </c>
-      <c r="J224" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K224" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L224" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M224">
-        <v>8000</v>
-      </c>
-      <c r="N224" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="O224" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O224"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O218"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ข้อมูลครุภัณฑ์/รายงานรายการครุภัณฑ์คงทนที่ยังไม่มีรูปภาพ.updated.xlsx
+++ b/ข้อมูลครุภัณฑ์/รายงานรายการครุภัณฑ์คงทนที่ยังไม่มีรูปภาพ.updated.xlsx
@@ -487,19 +487,19 @@
         <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
         <v>2</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
       <c r="F4">
         <v>4</v>
       </c>
       <c r="G4" t="str">
-        <v>0.0%</v>
+        <v>33.3%</v>
       </c>
     </row>
     <row r="5">
@@ -976,13 +976,13 @@
         <v>52</v>
       </c>
       <c r="E25">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="F25">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G25" t="str">
-        <v>32.7%</v>
+        <v>86.5%</v>
       </c>
     </row>
     <row r="26">
@@ -993,19 +993,19 @@
         <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E26">
         <v>17</v>
       </c>
       <c r="F26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G26" t="str">
-        <v>89.5%</v>
+        <v>100.0%</v>
       </c>
     </row>
     <row r="27">
@@ -1114,13 +1114,13 @@
         <v>373</v>
       </c>
       <c r="E31">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="F31">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="G31" t="str">
-        <v>41.8%</v>
+        <v>49.9%</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M48"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -1403,7 +1403,7 @@
         <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C7" t="str">
-        <v>EQ-AI-0001</v>
+        <v>EQ-AI-0003</v>
       </c>
       <c r="D7" t="str">
         <v>จอ LED 40 นิ้ว</v>
@@ -1444,7 +1444,7 @@
         <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C8" t="str">
-        <v>EQ-AI-0003</v>
+        <v>EQ-AI-0005</v>
       </c>
       <c r="D8" t="str">
         <v>แทบเล็ตสำหรับหุ่น AI</v>
@@ -2879,28 +2879,28 @@
         <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="C43" t="str">
-        <v>EQ-STI-0006</v>
+        <v>EQ-STI-0049</v>
       </c>
       <c r="D43" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="E43" t="str">
         <v>3B Scientific</v>
       </c>
       <c r="F43" t="str">
-        <v>P101</v>
+        <v>P100 Wound Care</v>
       </c>
       <c r="G43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H43">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I43" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J43" t="str">
-        <v>1-B9701-FA17-65450010004/037-68 ถึง 1-B9701-FA17-65450010004/040-68 (มี 4 เลข)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (12-1/2) ถึง 2-B9701-FA17-65450010002/001-67 (12-2/2) (มี 2 เลข)</v>
       </c>
       <c r="K43" t="str">
         <v>-</v>
@@ -2917,34 +2917,34 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C44" t="str">
-        <v>EQ-STI-0010</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="D44" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="E44" t="str">
-        <v>Nasco Life/form</v>
+        <v>Cardionics</v>
       </c>
       <c r="F44" t="str">
-        <v>LF01034</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="G44">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H44">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I44" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J44" t="str">
-        <v>1-B9701-FA17-65450010004/041-68 ถึง 1-B9701-FA17-65450010004/044-68 (มี 4 เลข)</v>
+        <v>1-B9701-FA17-65450010004/055-68 ถึง 1-B9701-FA17-65450010004/064-68 (มี 10 เลข)</v>
       </c>
       <c r="K44" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="L44" t="str">
         <v/>
@@ -2958,31 +2958,31 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C45" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="D45" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="E45" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="F45" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="G45">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H45">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I45" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J45" t="str">
-        <v>1-B9701-FN17-65450010002/004-68 ถึง 1-B9701-FN17-65450010002/023-68 (มี 20 เลข)</v>
+        <v>1-B9701-FA18-74400010005/001-68 ถึง 1-B9701-FA18-74400010005/010-68 (มี 10 เลข)</v>
       </c>
       <c r="K45" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2999,31 +2999,31 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C46" t="str">
-        <v>EQ-STI-0049</v>
+        <v>EQ-SAM-0021</v>
       </c>
       <c r="D46" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
       </c>
       <c r="E46" t="str">
-        <v>3B Scientific</v>
+        <v>Cardionics</v>
       </c>
       <c r="F46" t="str">
-        <v>P100 Wound Care</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="G46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I46" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J46" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (12-1/2) ถึง 2-B9701-FA17-65450010002/001-67 (12-2/2) (มี 2 เลข)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (21-1/1)</v>
       </c>
       <c r="K46" t="str">
         <v>-</v>
@@ -3040,31 +3040,31 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C47" t="str">
-        <v>EQ-FMS-0001</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="D47" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="E47" t="str">
-        <v>3B Scientific</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="F47" t="str">
-        <v>101-7140-8Y (KERi)</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="G47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I47" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J47" t="str">
-        <v>1-B9701-FA17-65450010004/001-68 ถึง 1-B9701-FA17-65450010004/002-68 (มี 2 เลข)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (42-1/1) ถึง 1-B9701-FN17-65450010002/003-68 (มี 4 เลข)</v>
       </c>
       <c r="K47" t="str">
         <v>-</v>
@@ -3081,31 +3081,31 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C48" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="D48" t="str">
-        <v>SAM</v>
+        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E48" t="str">
-        <v>Cardionics</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="F48" t="str">
-        <v>718-8804 SAM</v>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="G48">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H48">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I48" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J48" t="str">
-        <v>1-B9701-FA17-65450010004/055-68 ถึง 1-B9701-FA17-65450010004/064-68 (มี 10 เลข)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (43-1/2) ถึง 2-B9701-FA17-65450010002/001-67 (43-2/2) (มี 2 เลข)</v>
       </c>
       <c r="K48" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -3114,183 +3114,19 @@
         <v/>
       </c>
       <c r="M48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C49" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="D49" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="E49" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="F49" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="G49">
-        <v>10</v>
-      </c>
-      <c r="H49">
-        <v>10</v>
-      </c>
-      <c r="I49" t="str">
-        <v>ยังไม่มีรูปภาพเลย (0%)</v>
-      </c>
-      <c r="J49" t="str">
-        <v>1-B9701-FA18-74400010005/001-68 ถึง 1-B9701-FA18-74400010005/010-68 (มี 10 เลข)</v>
-      </c>
-      <c r="K49" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="L49" t="str">
-        <v/>
-      </c>
-      <c r="M49" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C50" t="str">
-        <v>EQ-SAM-0021</v>
-      </c>
-      <c r="D50" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
-      </c>
-      <c r="E50" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="F50" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50" t="str">
-        <v>ยังไม่มีรูปภาพเลย (0%)</v>
-      </c>
-      <c r="J50" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (21-1/1)</v>
-      </c>
-      <c r="K50" t="str">
-        <v>-</v>
-      </c>
-      <c r="L50" t="str">
-        <v/>
-      </c>
-      <c r="M50" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C51" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="D51" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="E51" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="F51" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="G51">
-        <v>4</v>
-      </c>
-      <c r="H51">
-        <v>4</v>
-      </c>
-      <c r="I51" t="str">
-        <v>ยังไม่มีรูปภาพเลย (0%)</v>
-      </c>
-      <c r="J51" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (42-1/1) ถึง 1-B9701-FN17-65450010002/003-68 (มี 4 เลข)</v>
-      </c>
-      <c r="K51" t="str">
-        <v>-</v>
-      </c>
-      <c r="L51" t="str">
-        <v/>
-      </c>
-      <c r="M51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C52" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="D52" t="str">
-        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="E52" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="F52" t="str">
-        <v>Patient Transfer Slide</v>
-      </c>
-      <c r="G52">
-        <v>2</v>
-      </c>
-      <c r="H52">
-        <v>2</v>
-      </c>
-      <c r="I52" t="str">
-        <v>ยังไม่มีรูปภาพเลย (0%)</v>
-      </c>
-      <c r="J52" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (43-1/2) ถึง 2-B9701-FA17-65450010002/001-67 (43-2/2) (มี 2 เลข)</v>
-      </c>
-      <c r="K52" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="L52" t="str">
-        <v/>
-      </c>
-      <c r="M52" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M48"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O218"/>
+  <dimension ref="A1:O188"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -3693,7 +3529,7 @@
         <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C9" t="str">
-        <v>EQ-AI-0001</v>
+        <v>EQ-AI-0003</v>
       </c>
       <c r="D9" t="str">
         <v>1-B9701-FA09-66600010001/003-68</v>
@@ -3726,7 +3562,7 @@
         <v>20000</v>
       </c>
       <c r="N9" t="str">
-        <v>EQ-AI-0001</v>
+        <v>EQ-AI-0003</v>
       </c>
       <c r="O9" t="str">
         <v/>
@@ -3740,7 +3576,7 @@
         <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C10" t="str">
-        <v>EQ-AI-0002</v>
+        <v>EQ-AI-0004</v>
       </c>
       <c r="D10" t="str">
         <v>1-B9701-FA09-66600010001/004-68</v>
@@ -3773,7 +3609,7 @@
         <v>20000</v>
       </c>
       <c r="N10" t="str">
-        <v>EQ-AI-0001</v>
+        <v>EQ-AI-0003</v>
       </c>
       <c r="O10" t="str">
         <v/>
@@ -3787,7 +3623,7 @@
         <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C11" t="str">
-        <v>EQ-AI-0003</v>
+        <v>EQ-AI-0005</v>
       </c>
       <c r="D11" t="str">
         <v>1-B9701-FN18-74400010005/001-68</v>
@@ -3820,7 +3656,7 @@
         <v>5000</v>
       </c>
       <c r="N11" t="str">
-        <v>EQ-AI-0003</v>
+        <v>EQ-AI-0005</v>
       </c>
       <c r="O11" t="str">
         <v/>
@@ -3834,7 +3670,7 @@
         <v>(หุ่น AI) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C12" t="str">
-        <v>EQ-AI-0004</v>
+        <v>EQ-AI-0006</v>
       </c>
       <c r="D12" t="str">
         <v>1-B9701-FN18-74400010005/002-68</v>
@@ -3867,7 +3703,7 @@
         <v>5000</v>
       </c>
       <c r="N12" t="str">
-        <v>EQ-AI-0003</v>
+        <v>EQ-AI-0005</v>
       </c>
       <c r="O12" t="str">
         <v/>
@@ -10790,13 +10626,13 @@
         <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="C160" t="str">
-        <v>EQ-STI-0006</v>
+        <v>EQ-STI-0049</v>
       </c>
       <c r="D160" t="str">
-        <v>1-B9701-FA17-65450010004/037-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (12-1/2)</v>
       </c>
       <c r="E160" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="F160">
         <v>1</v>
@@ -10805,7 +10641,7 @@
         <v>3B Scientific</v>
       </c>
       <c r="H160" t="str">
-        <v>P101</v>
+        <v>P100 Wound Care</v>
       </c>
       <c r="I160" t="str">
         <v>-</v>
@@ -10820,10 +10656,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M160">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="N160" t="str">
-        <v>EQ-STI-0006</v>
+        <v>EQ-STI-0049</v>
       </c>
       <c r="O160" t="str">
         <v/>
@@ -10837,13 +10673,13 @@
         <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
       </c>
       <c r="C161" t="str">
-        <v>EQ-STI-0007</v>
+        <v>EQ-STI-0050</v>
       </c>
       <c r="D161" t="str">
-        <v>1-B9701-FA17-65450010004/038-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (12-2/2)</v>
       </c>
       <c r="E161" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
       </c>
       <c r="F161">
         <v>2</v>
@@ -10852,7 +10688,7 @@
         <v>3B Scientific</v>
       </c>
       <c r="H161" t="str">
-        <v>P101</v>
+        <v>P100 Wound Care</v>
       </c>
       <c r="I161" t="str">
         <v>-</v>
@@ -10867,10 +10703,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M161">
-        <v>25000</v>
+        <v>40000</v>
       </c>
       <c r="N161" t="str">
-        <v>EQ-STI-0006</v>
+        <v>EQ-STI-0049</v>
       </c>
       <c r="O161" t="str">
         <v/>
@@ -10881,31 +10717,31 @@
         <v>161</v>
       </c>
       <c r="B162" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C162" t="str">
-        <v>EQ-STI-0008</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="D162" t="str">
-        <v>1-B9701-FA17-65450010004/039-68</v>
+        <v>1-B9701-FA17-65450010004/055-68</v>
       </c>
       <c r="E162" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="F162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G162" t="str">
-        <v>3B Scientific</v>
+        <v>Cardionics</v>
       </c>
       <c r="H162" t="str">
-        <v>P101</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I162" t="str">
         <v>-</v>
       </c>
       <c r="J162" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K162" t="str">
         <v>พร้อมใช้งาน</v>
@@ -10914,10 +10750,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M162">
-        <v>25000</v>
+        <v>735000</v>
       </c>
       <c r="N162" t="str">
-        <v>EQ-STI-0006</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="O162" t="str">
         <v/>
@@ -10928,31 +10764,31 @@
         <v>162</v>
       </c>
       <c r="B163" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C163" t="str">
-        <v>EQ-STI-0009</v>
+        <v>EQ-SAM-0002</v>
       </c>
       <c r="D163" t="str">
-        <v>1-B9701-FA17-65450010004/040-68</v>
+        <v>1-B9701-FA17-65450010004/056-68</v>
       </c>
       <c r="E163" t="str">
-        <v>หุ่นแขนฝึกการเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="F163">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G163" t="str">
-        <v>3B Scientific</v>
+        <v>Cardionics</v>
       </c>
       <c r="H163" t="str">
-        <v>P101</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I163" t="str">
         <v>-</v>
       </c>
       <c r="J163" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K163" t="str">
         <v>พร้อมใช้งาน</v>
@@ -10961,10 +10797,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M163">
-        <v>25000</v>
+        <v>735000</v>
       </c>
       <c r="N163" t="str">
-        <v>EQ-STI-0006</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="O163" t="str">
         <v/>
@@ -10975,31 +10811,31 @@
         <v>163</v>
       </c>
       <c r="B164" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C164" t="str">
-        <v>EQ-STI-0010</v>
+        <v>EQ-SAM-0003</v>
       </c>
       <c r="D164" t="str">
-        <v>1-B9701-FA17-65450010004/041-68</v>
+        <v>1-B9701-FA17-65450010004/057-68</v>
       </c>
       <c r="E164" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G164" t="str">
-        <v>Nasco Life/form</v>
+        <v>Cardionics</v>
       </c>
       <c r="H164" t="str">
-        <v>LF01034</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I164" t="str">
         <v>-</v>
       </c>
       <c r="J164" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K164" t="str">
         <v>พร้อมใช้งาน</v>
@@ -11008,10 +10844,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M164">
-        <v>30000</v>
+        <v>735000</v>
       </c>
       <c r="N164" t="str">
-        <v>EQ-STI-0010</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="O164" t="str">
         <v/>
@@ -11022,31 +10858,31 @@
         <v>164</v>
       </c>
       <c r="B165" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C165" t="str">
-        <v>EQ-STI-0011</v>
+        <v>EQ-SAM-0004</v>
       </c>
       <c r="D165" t="str">
-        <v>1-B9701-FA17-65450010004/042-68</v>
+        <v>1-B9701-FA17-65450010004/058-68</v>
       </c>
       <c r="E165" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="F165">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G165" t="str">
-        <v>Nasco Life/form</v>
+        <v>Cardionics</v>
       </c>
       <c r="H165" t="str">
-        <v>LF01034</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I165" t="str">
         <v>-</v>
       </c>
       <c r="J165" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K165" t="str">
         <v>พร้อมใช้งาน</v>
@@ -11055,10 +10891,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M165">
-        <v>30000</v>
+        <v>735000</v>
       </c>
       <c r="N165" t="str">
-        <v>EQ-STI-0010</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="O165" t="str">
         <v/>
@@ -11069,31 +10905,31 @@
         <v>165</v>
       </c>
       <c r="B166" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C166" t="str">
-        <v>EQ-STI-0012</v>
+        <v>EQ-SAM-0005</v>
       </c>
       <c r="D166" t="str">
-        <v>1-B9701-FA17-65450010004/043-68</v>
+        <v>1-B9701-FA17-65450010004/059-68</v>
       </c>
       <c r="E166" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="F166">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G166" t="str">
-        <v>Nasco Life/form</v>
+        <v>Cardionics</v>
       </c>
       <c r="H166" t="str">
-        <v>LF01034</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I166" t="str">
         <v>-</v>
       </c>
       <c r="J166" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K166" t="str">
         <v>พร้อมใช้งาน</v>
@@ -11102,10 +10938,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M166">
-        <v>30000</v>
+        <v>735000</v>
       </c>
       <c r="N166" t="str">
-        <v>EQ-STI-0010</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="O166" t="str">
         <v/>
@@ -11116,31 +10952,31 @@
         <v>166</v>
       </c>
       <c r="B167" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C167" t="str">
-        <v>EQ-STI-0013</v>
+        <v>EQ-SAM-0006</v>
       </c>
       <c r="D167" t="str">
-        <v>1-B9701-FA17-65450010004/044-68</v>
+        <v>1-B9701-FA17-65450010004/060-68</v>
       </c>
       <c r="E167" t="str">
-        <v>หุ่นขาฝึกเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="F167">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G167" t="str">
-        <v>Nasco Life/form</v>
+        <v>Cardionics</v>
       </c>
       <c r="H167" t="str">
-        <v>LF01034</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I167" t="str">
         <v>-</v>
       </c>
       <c r="J167" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K167" t="str">
         <v>พร้อมใช้งาน</v>
@@ -11149,10 +10985,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M167">
-        <v>30000</v>
+        <v>735000</v>
       </c>
       <c r="N167" t="str">
-        <v>EQ-STI-0010</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="O167" t="str">
         <v/>
@@ -11163,25 +10999,25 @@
         <v>167</v>
       </c>
       <c r="B168" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C168" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0007</v>
       </c>
       <c r="D168" t="str">
-        <v>1-B9701-FN17-65450010002/004-68</v>
+        <v>1-B9701-FA17-65450010004/061-68</v>
       </c>
       <c r="E168" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="F168">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G168" t="str">
-        <v>Nasco Life/form</v>
+        <v>Cardionics</v>
       </c>
       <c r="H168" t="str">
-        <v>LF01043</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I168" t="str">
         <v>-</v>
@@ -11196,10 +11032,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M168">
-        <v>4700</v>
+        <v>735000</v>
       </c>
       <c r="N168" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="O168" t="str">
         <v/>
@@ -11210,25 +11046,25 @@
         <v>168</v>
       </c>
       <c r="B169" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C169" t="str">
-        <v>EQ-STI-0025</v>
+        <v>EQ-SAM-0008</v>
       </c>
       <c r="D169" t="str">
-        <v>1-B9701-FN17-65450010002/005-68</v>
+        <v>1-B9701-FA17-65450010004/062-68</v>
       </c>
       <c r="E169" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="F169">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G169" t="str">
-        <v>Nasco Life/form</v>
+        <v>Cardionics</v>
       </c>
       <c r="H169" t="str">
-        <v>LF01043</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I169" t="str">
         <v>-</v>
@@ -11243,10 +11079,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M169">
-        <v>4700</v>
+        <v>735000</v>
       </c>
       <c r="N169" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="O169" t="str">
         <v/>
@@ -11257,25 +11093,25 @@
         <v>169</v>
       </c>
       <c r="B170" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C170" t="str">
-        <v>EQ-STI-0026</v>
+        <v>EQ-SAM-0009</v>
       </c>
       <c r="D170" t="str">
-        <v>1-B9701-FN17-65450010002/006-68</v>
+        <v>1-B9701-FA17-65450010004/063-68</v>
       </c>
       <c r="E170" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="F170">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="G170" t="str">
-        <v>Nasco Life/form</v>
+        <v>Cardionics</v>
       </c>
       <c r="H170" t="str">
-        <v>LF01043</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I170" t="str">
         <v>-</v>
@@ -11290,10 +11126,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M170">
-        <v>4700</v>
+        <v>735000</v>
       </c>
       <c r="N170" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="O170" t="str">
         <v/>
@@ -11304,25 +11140,25 @@
         <v>170</v>
       </c>
       <c r="B171" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C171" t="str">
-        <v>EQ-STI-0027</v>
+        <v>EQ-SAM-0010</v>
       </c>
       <c r="D171" t="str">
-        <v>1-B9701-FN17-65450010002/007-68</v>
+        <v>1-B9701-FA17-65450010004/064-68</v>
       </c>
       <c r="E171" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM</v>
       </c>
       <c r="F171">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G171" t="str">
-        <v>Nasco Life/form</v>
+        <v>Cardionics</v>
       </c>
       <c r="H171" t="str">
-        <v>LF01043</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I171" t="str">
         <v>-</v>
@@ -11337,10 +11173,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M171">
-        <v>4700</v>
+        <v>735000</v>
       </c>
       <c r="N171" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0001</v>
       </c>
       <c r="O171" t="str">
         <v/>
@@ -11351,25 +11187,25 @@
         <v>171</v>
       </c>
       <c r="B172" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C172" t="str">
-        <v>EQ-STI-0028</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="D172" t="str">
-        <v>1-B9701-FN17-65450010002/008-68</v>
+        <v>1-B9701-FA18-74400010005/001-68</v>
       </c>
       <c r="E172" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F172">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G172" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="H172" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I172" t="str">
         <v>-</v>
@@ -11384,10 +11220,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M172">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="N172" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O172" t="str">
         <v/>
@@ -11398,25 +11234,25 @@
         <v>172</v>
       </c>
       <c r="B173" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C173" t="str">
-        <v>EQ-STI-0029</v>
+        <v>EQ-SAM-0012</v>
       </c>
       <c r="D173" t="str">
-        <v>1-B9701-FN17-65450010002/009-68</v>
+        <v>1-B9701-FA18-74400010005/002-68</v>
       </c>
       <c r="E173" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F173">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G173" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="H173" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I173" t="str">
         <v>-</v>
@@ -11431,10 +11267,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M173">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="N173" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O173" t="str">
         <v/>
@@ -11445,25 +11281,25 @@
         <v>173</v>
       </c>
       <c r="B174" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C174" t="str">
-        <v>EQ-STI-0030</v>
+        <v>EQ-SAM-0013</v>
       </c>
       <c r="D174" t="str">
-        <v>1-B9701-FN17-65450010002/010-68</v>
+        <v>1-B9701-FA18-74400010005/003-68</v>
       </c>
       <c r="E174" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F174">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G174" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="H174" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I174" t="str">
         <v>-</v>
@@ -11478,10 +11314,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M174">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="N174" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O174" t="str">
         <v/>
@@ -11492,25 +11328,25 @@
         <v>174</v>
       </c>
       <c r="B175" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C175" t="str">
-        <v>EQ-STI-0031</v>
+        <v>EQ-SAM-0014</v>
       </c>
       <c r="D175" t="str">
-        <v>1-B9701-FN17-65450010002/011-68</v>
+        <v>1-B9701-FA18-74400010005/004-68</v>
       </c>
       <c r="E175" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F175">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G175" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="H175" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I175" t="str">
         <v>-</v>
@@ -11525,10 +11361,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M175">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="N175" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O175" t="str">
         <v/>
@@ -11539,25 +11375,25 @@
         <v>175</v>
       </c>
       <c r="B176" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C176" t="str">
-        <v>EQ-STI-0032</v>
+        <v>EQ-SAM-0015</v>
       </c>
       <c r="D176" t="str">
-        <v>1-B9701-FN17-65450010002/012-68</v>
+        <v>1-B9701-FA18-74400010005/005-68</v>
       </c>
       <c r="E176" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F176">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G176" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="H176" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I176" t="str">
         <v>-</v>
@@ -11572,10 +11408,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M176">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="N176" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O176" t="str">
         <v/>
@@ -11586,25 +11422,25 @@
         <v>176</v>
       </c>
       <c r="B177" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C177" t="str">
-        <v>EQ-STI-0033</v>
+        <v>EQ-SAM-0016</v>
       </c>
       <c r="D177" t="str">
-        <v>1-B9701-FN17-65450010002/013-68</v>
+        <v>1-B9701-FA18-74400010005/006-68</v>
       </c>
       <c r="E177" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F177">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G177" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="H177" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I177" t="str">
         <v>-</v>
@@ -11619,10 +11455,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M177">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="N177" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O177" t="str">
         <v/>
@@ -11633,25 +11469,25 @@
         <v>177</v>
       </c>
       <c r="B178" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C178" t="str">
-        <v>EQ-STI-0034</v>
+        <v>EQ-SAM-0017</v>
       </c>
       <c r="D178" t="str">
-        <v>1-B9701-FN17-65450010002/014-68</v>
+        <v>1-B9701-FA18-74400010005/007-68</v>
       </c>
       <c r="E178" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F178">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G178" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="H178" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I178" t="str">
         <v>-</v>
@@ -11666,10 +11502,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M178">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="N178" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O178" t="str">
         <v/>
@@ -11680,25 +11516,25 @@
         <v>178</v>
       </c>
       <c r="B179" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C179" t="str">
-        <v>EQ-STI-0035</v>
+        <v>EQ-SAM-0018</v>
       </c>
       <c r="D179" t="str">
-        <v>1-B9701-FN17-65450010002/015-68</v>
+        <v>1-B9701-FA18-74400010005/008-68</v>
       </c>
       <c r="E179" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F179">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G179" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="H179" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I179" t="str">
         <v>-</v>
@@ -11713,10 +11549,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M179">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="N179" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O179" t="str">
         <v/>
@@ -11727,25 +11563,25 @@
         <v>179</v>
       </c>
       <c r="B180" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C180" t="str">
-        <v>EQ-STI-0036</v>
+        <v>EQ-SAM-0019</v>
       </c>
       <c r="D180" t="str">
-        <v>1-B9701-FN17-65450010002/016-68</v>
+        <v>1-B9701-FA18-74400010005/009-68</v>
       </c>
       <c r="E180" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F180">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G180" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="H180" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I180" t="str">
         <v>-</v>
@@ -11760,10 +11596,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M180">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="N180" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O180" t="str">
         <v/>
@@ -11774,25 +11610,25 @@
         <v>180</v>
       </c>
       <c r="B181" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C181" t="str">
-        <v>EQ-STI-0037</v>
+        <v>EQ-SAM-0020</v>
       </c>
       <c r="D181" t="str">
-        <v>1-B9701-FN17-65450010002/017-68</v>
+        <v>1-B9701-FA18-74400010005/010-68</v>
       </c>
       <c r="E181" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F181">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G181" t="str">
-        <v>Nasco Life/form</v>
+        <v>Apple</v>
       </c>
       <c r="H181" t="str">
-        <v>LF01043</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I181" t="str">
         <v>-</v>
@@ -11807,10 +11643,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M181">
-        <v>4700</v>
+        <v>15000</v>
       </c>
       <c r="N181" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O181" t="str">
         <v/>
@@ -11821,25 +11657,25 @@
         <v>181</v>
       </c>
       <c r="B182" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C182" t="str">
-        <v>EQ-STI-0038</v>
+        <v>EQ-SAM-0021</v>
       </c>
       <c r="D182" t="str">
-        <v>1-B9701-FN17-65450010002/018-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (21-1/1)</v>
       </c>
       <c r="E182" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
       </c>
       <c r="F182">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G182" t="str">
-        <v>Nasco Life/form</v>
+        <v>Cardionics</v>
       </c>
       <c r="H182" t="str">
-        <v>LF01043</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I182" t="str">
         <v>-</v>
@@ -11854,10 +11690,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M182">
-        <v>4700</v>
+        <v>200000</v>
       </c>
       <c r="N182" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-SAM-0021</v>
       </c>
       <c r="O182" t="str">
         <v/>
@@ -11868,25 +11704,25 @@
         <v>182</v>
       </c>
       <c r="B183" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C183" t="str">
-        <v>EQ-STI-0039</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="D183" t="str">
-        <v>1-B9701-FN17-65450010002/019-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
       </c>
       <c r="E183" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F183">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G183" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H183" t="str">
-        <v>LF01043</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I183" t="str">
         <v>-</v>
@@ -11901,10 +11737,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M183">
-        <v>4700</v>
+        <v>7000</v>
       </c>
       <c r="N183" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O183" t="str">
         <v/>
@@ -11915,25 +11751,25 @@
         <v>183</v>
       </c>
       <c r="B184" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C184" t="str">
-        <v>EQ-STI-0040</v>
+        <v>EQ-TRS-0002</v>
       </c>
       <c r="D184" t="str">
-        <v>1-B9701-FN17-65450010002/020-68</v>
+        <v>1-B9701-FN17-65450010002/001-68</v>
       </c>
       <c r="E184" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F184">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="G184" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H184" t="str">
-        <v>LF01043</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I184" t="str">
         <v>-</v>
@@ -11948,10 +11784,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M184">
-        <v>4700</v>
+        <v>1000</v>
       </c>
       <c r="N184" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O184" t="str">
         <v/>
@@ -11962,25 +11798,25 @@
         <v>184</v>
       </c>
       <c r="B185" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C185" t="str">
-        <v>EQ-STI-0041</v>
+        <v>EQ-TRS-0003</v>
       </c>
       <c r="D185" t="str">
-        <v>1-B9701-FN17-65450010002/021-68</v>
+        <v>1-B9701-FN17-65450010002/002-68</v>
       </c>
       <c r="E185" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F185">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G185" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H185" t="str">
-        <v>LF01043</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I185" t="str">
         <v>-</v>
@@ -11995,10 +11831,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M185">
-        <v>4700</v>
+        <v>1000</v>
       </c>
       <c r="N185" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O185" t="str">
         <v/>
@@ -12009,25 +11845,25 @@
         <v>185</v>
       </c>
       <c r="B186" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C186" t="str">
-        <v>EQ-STI-0042</v>
+        <v>EQ-TRS-0004</v>
       </c>
       <c r="D186" t="str">
-        <v>1-B9701-FN17-65450010002/022-68</v>
+        <v>1-B9701-FN17-65450010002/003-68</v>
       </c>
       <c r="E186" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F186">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G186" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H186" t="str">
-        <v>LF01043</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I186" t="str">
         <v>-</v>
@@ -12042,10 +11878,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M186">
-        <v>4700</v>
+        <v>1000</v>
       </c>
       <c r="N186" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O186" t="str">
         <v/>
@@ -12056,25 +11892,25 @@
         <v>186</v>
       </c>
       <c r="B187" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C187" t="str">
-        <v>EQ-STI-0043</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="D187" t="str">
-        <v>1-B9701-FN17-65450010002/023-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (43-1/2)</v>
       </c>
       <c r="E187" t="str">
-        <v>แผ่นผิวหนังฝึกเย็บแผล</v>
+        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="F187">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="G187" t="str">
-        <v>Nasco Life/form</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H187" t="str">
-        <v>LF01043</v>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="I187" t="str">
         <v>-</v>
@@ -12089,10 +11925,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M187">
-        <v>4700</v>
+        <v>8000</v>
       </c>
       <c r="N187" t="str">
-        <v>EQ-STI-0024</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="O187" t="str">
         <v/>
@@ -12103,31 +11939,31 @@
         <v>187</v>
       </c>
       <c r="B188" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C188" t="str">
-        <v>EQ-STI-0049</v>
+        <v>EQ-TRS-0006</v>
       </c>
       <c r="D188" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (12-1/2)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (43-2/2)</v>
       </c>
       <c r="E188" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
+        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="F188">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G188" t="str">
-        <v>3B Scientific</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H188" t="str">
-        <v>P100 Wound Care</v>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="I188" t="str">
         <v>-</v>
       </c>
       <c r="J188" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="K188" t="str">
         <v>พร้อมใช้งาน</v>
@@ -12136,1428 +11972,18 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M188">
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="N188" t="str">
-        <v>EQ-STI-0049</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="O188" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189">
-        <v>188</v>
-      </c>
-      <c r="B189" t="str">
-        <v>หุ่นฝึกทำแผล การดูแลแผลและเย็บแผล</v>
-      </c>
-      <c r="C189" t="str">
-        <v>EQ-STI-0050</v>
-      </c>
-      <c r="D189" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (12-2/2)</v>
-      </c>
-      <c r="E189" t="str">
-        <v>หุ่นฝึกการดูแลแผลผ่าตัดและฝึกทักษะการพันแผล</v>
-      </c>
-      <c r="F189">
-        <v>2</v>
-      </c>
-      <c r="G189" t="str">
-        <v>3B Scientific</v>
-      </c>
-      <c r="H189" t="str">
-        <v>P100 Wound Care</v>
-      </c>
-      <c r="I189" t="str">
-        <v>-</v>
-      </c>
-      <c r="J189" t="str">
-        <v>-</v>
-      </c>
-      <c r="K189" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L189" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M189">
-        <v>40000</v>
-      </c>
-      <c r="N189" t="str">
-        <v>EQ-STI-0049</v>
-      </c>
-      <c r="O189" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190">
-        <v>189</v>
-      </c>
-      <c r="B190" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
-      </c>
-      <c r="C190" t="str">
-        <v>EQ-FMS-0001</v>
-      </c>
-      <c r="D190" t="str">
-        <v>1-B9701-FA17-65450010004/001-68</v>
-      </c>
-      <c r="E190" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง</v>
-      </c>
-      <c r="F190">
-        <v>1</v>
-      </c>
-      <c r="G190" t="str">
-        <v>3B Scientific</v>
-      </c>
-      <c r="H190" t="str">
-        <v>101-7140-8Y (KERi)</v>
-      </c>
-      <c r="I190" t="str">
-        <v>-</v>
-      </c>
-      <c r="J190" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K190" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L190" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M190">
-        <v>2765000</v>
-      </c>
-      <c r="N190" t="str">
-        <v>EQ-FMS-0001</v>
-      </c>
-      <c r="O190" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191">
-        <v>190</v>
-      </c>
-      <c r="B191" t="str">
-        <v>หุ่นฝึกปฏิบัติการ</v>
-      </c>
-      <c r="C191" t="str">
-        <v>EQ-FMS-0002</v>
-      </c>
-      <c r="D191" t="str">
-        <v>1-B9701-FA17-65450010004/002-68</v>
-      </c>
-      <c r="E191" t="str">
-        <v>หุ่นฝึกทักษะการพยาบาลขั้นสูง</v>
-      </c>
-      <c r="F191">
-        <v>2</v>
-      </c>
-      <c r="G191" t="str">
-        <v>3B Scientific</v>
-      </c>
-      <c r="H191" t="str">
-        <v>101-7140-8Y (KERi)</v>
-      </c>
-      <c r="I191" t="str">
-        <v>-</v>
-      </c>
-      <c r="J191" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K191" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L191" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M191">
-        <v>2765000</v>
-      </c>
-      <c r="N191" t="str">
-        <v>EQ-FMS-0001</v>
-      </c>
-      <c r="O191" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192">
-        <v>191</v>
-      </c>
-      <c r="B192" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C192" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="D192" t="str">
-        <v>1-B9701-FA17-65450010004/055-68</v>
-      </c>
-      <c r="E192" t="str">
-        <v>SAM</v>
-      </c>
-      <c r="F192">
-        <v>1</v>
-      </c>
-      <c r="G192" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H192" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I192" t="str">
-        <v>-</v>
-      </c>
-      <c r="J192" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K192" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L192" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M192">
-        <v>735000</v>
-      </c>
-      <c r="N192" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="O192" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193">
-        <v>192</v>
-      </c>
-      <c r="B193" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C193" t="str">
-        <v>EQ-SAM-0002</v>
-      </c>
-      <c r="D193" t="str">
-        <v>1-B9701-FA17-65450010004/056-68</v>
-      </c>
-      <c r="E193" t="str">
-        <v>SAM</v>
-      </c>
-      <c r="F193">
-        <v>2</v>
-      </c>
-      <c r="G193" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H193" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I193" t="str">
-        <v>-</v>
-      </c>
-      <c r="J193" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K193" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L193" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M193">
-        <v>735000</v>
-      </c>
-      <c r="N193" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="O193" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194">
-        <v>193</v>
-      </c>
-      <c r="B194" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C194" t="str">
-        <v>EQ-SAM-0003</v>
-      </c>
-      <c r="D194" t="str">
-        <v>1-B9701-FA17-65450010004/057-68</v>
-      </c>
-      <c r="E194" t="str">
-        <v>SAM</v>
-      </c>
-      <c r="F194">
-        <v>3</v>
-      </c>
-      <c r="G194" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H194" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I194" t="str">
-        <v>-</v>
-      </c>
-      <c r="J194" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K194" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L194" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M194">
-        <v>735000</v>
-      </c>
-      <c r="N194" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="O194" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195">
-        <v>194</v>
-      </c>
-      <c r="B195" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C195" t="str">
-        <v>EQ-SAM-0004</v>
-      </c>
-      <c r="D195" t="str">
-        <v>1-B9701-FA17-65450010004/058-68</v>
-      </c>
-      <c r="E195" t="str">
-        <v>SAM</v>
-      </c>
-      <c r="F195">
-        <v>4</v>
-      </c>
-      <c r="G195" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H195" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I195" t="str">
-        <v>-</v>
-      </c>
-      <c r="J195" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K195" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L195" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M195">
-        <v>735000</v>
-      </c>
-      <c r="N195" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="O195" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196">
-        <v>195</v>
-      </c>
-      <c r="B196" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C196" t="str">
-        <v>EQ-SAM-0005</v>
-      </c>
-      <c r="D196" t="str">
-        <v>1-B9701-FA17-65450010004/059-68</v>
-      </c>
-      <c r="E196" t="str">
-        <v>SAM</v>
-      </c>
-      <c r="F196">
-        <v>5</v>
-      </c>
-      <c r="G196" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H196" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I196" t="str">
-        <v>-</v>
-      </c>
-      <c r="J196" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K196" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L196" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M196">
-        <v>735000</v>
-      </c>
-      <c r="N196" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="O196" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197">
-        <v>196</v>
-      </c>
-      <c r="B197" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C197" t="str">
-        <v>EQ-SAM-0006</v>
-      </c>
-      <c r="D197" t="str">
-        <v>1-B9701-FA17-65450010004/060-68</v>
-      </c>
-      <c r="E197" t="str">
-        <v>SAM</v>
-      </c>
-      <c r="F197">
-        <v>6</v>
-      </c>
-      <c r="G197" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H197" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I197" t="str">
-        <v>-</v>
-      </c>
-      <c r="J197" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K197" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L197" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M197">
-        <v>735000</v>
-      </c>
-      <c r="N197" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="O197" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198">
-        <v>197</v>
-      </c>
-      <c r="B198" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C198" t="str">
-        <v>EQ-SAM-0007</v>
-      </c>
-      <c r="D198" t="str">
-        <v>1-B9701-FA17-65450010004/061-68</v>
-      </c>
-      <c r="E198" t="str">
-        <v>SAM</v>
-      </c>
-      <c r="F198">
-        <v>7</v>
-      </c>
-      <c r="G198" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H198" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I198" t="str">
-        <v>-</v>
-      </c>
-      <c r="J198" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K198" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L198" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M198">
-        <v>735000</v>
-      </c>
-      <c r="N198" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="O198" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199">
-        <v>198</v>
-      </c>
-      <c r="B199" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C199" t="str">
-        <v>EQ-SAM-0008</v>
-      </c>
-      <c r="D199" t="str">
-        <v>1-B9701-FA17-65450010004/062-68</v>
-      </c>
-      <c r="E199" t="str">
-        <v>SAM</v>
-      </c>
-      <c r="F199">
-        <v>8</v>
-      </c>
-      <c r="G199" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H199" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I199" t="str">
-        <v>-</v>
-      </c>
-      <c r="J199" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K199" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L199" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M199">
-        <v>735000</v>
-      </c>
-      <c r="N199" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="O199" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200">
-        <v>199</v>
-      </c>
-      <c r="B200" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C200" t="str">
-        <v>EQ-SAM-0009</v>
-      </c>
-      <c r="D200" t="str">
-        <v>1-B9701-FA17-65450010004/063-68</v>
-      </c>
-      <c r="E200" t="str">
-        <v>SAM</v>
-      </c>
-      <c r="F200">
-        <v>9</v>
-      </c>
-      <c r="G200" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H200" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I200" t="str">
-        <v>-</v>
-      </c>
-      <c r="J200" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K200" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L200" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M200">
-        <v>735000</v>
-      </c>
-      <c r="N200" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="O200" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201">
-        <v>200</v>
-      </c>
-      <c r="B201" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C201" t="str">
-        <v>EQ-SAM-0010</v>
-      </c>
-      <c r="D201" t="str">
-        <v>1-B9701-FA17-65450010004/064-68</v>
-      </c>
-      <c r="E201" t="str">
-        <v>SAM</v>
-      </c>
-      <c r="F201">
-        <v>10</v>
-      </c>
-      <c r="G201" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H201" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I201" t="str">
-        <v>-</v>
-      </c>
-      <c r="J201" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K201" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L201" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M201">
-        <v>735000</v>
-      </c>
-      <c r="N201" t="str">
-        <v>EQ-SAM-0001</v>
-      </c>
-      <c r="O201" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202">
-        <v>201</v>
-      </c>
-      <c r="B202" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C202" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="D202" t="str">
-        <v>1-B9701-FA18-74400010005/001-68</v>
-      </c>
-      <c r="E202" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F202">
-        <v>1</v>
-      </c>
-      <c r="G202" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H202" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I202" t="str">
-        <v>-</v>
-      </c>
-      <c r="J202" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K202" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L202" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M202">
-        <v>15000</v>
-      </c>
-      <c r="N202" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O202" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203">
-        <v>202</v>
-      </c>
-      <c r="B203" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C203" t="str">
-        <v>EQ-SAM-0012</v>
-      </c>
-      <c r="D203" t="str">
-        <v>1-B9701-FA18-74400010005/002-68</v>
-      </c>
-      <c r="E203" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F203">
-        <v>2</v>
-      </c>
-      <c r="G203" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H203" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I203" t="str">
-        <v>-</v>
-      </c>
-      <c r="J203" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K203" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L203" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M203">
-        <v>15000</v>
-      </c>
-      <c r="N203" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O203" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204">
-        <v>203</v>
-      </c>
-      <c r="B204" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C204" t="str">
-        <v>EQ-SAM-0013</v>
-      </c>
-      <c r="D204" t="str">
-        <v>1-B9701-FA18-74400010005/003-68</v>
-      </c>
-      <c r="E204" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F204">
-        <v>3</v>
-      </c>
-      <c r="G204" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H204" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I204" t="str">
-        <v>-</v>
-      </c>
-      <c r="J204" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K204" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L204" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M204">
-        <v>15000</v>
-      </c>
-      <c r="N204" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O204" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205">
-        <v>204</v>
-      </c>
-      <c r="B205" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C205" t="str">
-        <v>EQ-SAM-0014</v>
-      </c>
-      <c r="D205" t="str">
-        <v>1-B9701-FA18-74400010005/004-68</v>
-      </c>
-      <c r="E205" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F205">
-        <v>4</v>
-      </c>
-      <c r="G205" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H205" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I205" t="str">
-        <v>-</v>
-      </c>
-      <c r="J205" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K205" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L205" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M205">
-        <v>15000</v>
-      </c>
-      <c r="N205" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O205" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206">
-        <v>205</v>
-      </c>
-      <c r="B206" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C206" t="str">
-        <v>EQ-SAM-0015</v>
-      </c>
-      <c r="D206" t="str">
-        <v>1-B9701-FA18-74400010005/005-68</v>
-      </c>
-      <c r="E206" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F206">
-        <v>5</v>
-      </c>
-      <c r="G206" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H206" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I206" t="str">
-        <v>-</v>
-      </c>
-      <c r="J206" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K206" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L206" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M206">
-        <v>15000</v>
-      </c>
-      <c r="N206" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O206" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207">
-        <v>206</v>
-      </c>
-      <c r="B207" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C207" t="str">
-        <v>EQ-SAM-0016</v>
-      </c>
-      <c r="D207" t="str">
-        <v>1-B9701-FA18-74400010005/006-68</v>
-      </c>
-      <c r="E207" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F207">
-        <v>6</v>
-      </c>
-      <c r="G207" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H207" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I207" t="str">
-        <v>-</v>
-      </c>
-      <c r="J207" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K207" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L207" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M207">
-        <v>15000</v>
-      </c>
-      <c r="N207" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O207" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208">
-        <v>207</v>
-      </c>
-      <c r="B208" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C208" t="str">
-        <v>EQ-SAM-0017</v>
-      </c>
-      <c r="D208" t="str">
-        <v>1-B9701-FA18-74400010005/007-68</v>
-      </c>
-      <c r="E208" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F208">
-        <v>7</v>
-      </c>
-      <c r="G208" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H208" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I208" t="str">
-        <v>-</v>
-      </c>
-      <c r="J208" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K208" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L208" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M208">
-        <v>15000</v>
-      </c>
-      <c r="N208" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O208" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209">
-        <v>208</v>
-      </c>
-      <c r="B209" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C209" t="str">
-        <v>EQ-SAM-0018</v>
-      </c>
-      <c r="D209" t="str">
-        <v>1-B9701-FA18-74400010005/008-68</v>
-      </c>
-      <c r="E209" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F209">
-        <v>8</v>
-      </c>
-      <c r="G209" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H209" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I209" t="str">
-        <v>-</v>
-      </c>
-      <c r="J209" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K209" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L209" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M209">
-        <v>15000</v>
-      </c>
-      <c r="N209" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O209" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210">
-        <v>209</v>
-      </c>
-      <c r="B210" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C210" t="str">
-        <v>EQ-SAM-0019</v>
-      </c>
-      <c r="D210" t="str">
-        <v>1-B9701-FA18-74400010005/009-68</v>
-      </c>
-      <c r="E210" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F210">
-        <v>9</v>
-      </c>
-      <c r="G210" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H210" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I210" t="str">
-        <v>-</v>
-      </c>
-      <c r="J210" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K210" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L210" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M210">
-        <v>15000</v>
-      </c>
-      <c r="N210" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O210" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211">
-        <v>210</v>
-      </c>
-      <c r="B211" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C211" t="str">
-        <v>EQ-SAM-0020</v>
-      </c>
-      <c r="D211" t="str">
-        <v>1-B9701-FA18-74400010005/010-68</v>
-      </c>
-      <c r="E211" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F211">
-        <v>10</v>
-      </c>
-      <c r="G211" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H211" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I211" t="str">
-        <v>-</v>
-      </c>
-      <c r="J211" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K211" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L211" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M211">
-        <v>15000</v>
-      </c>
-      <c r="N211" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O211" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212">
-        <v>211</v>
-      </c>
-      <c r="B212" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C212" t="str">
-        <v>EQ-SAM-0021</v>
-      </c>
-      <c r="D212" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (21-1/1)</v>
-      </c>
-      <c r="E212" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
-      </c>
-      <c r="F212">
-        <v>1</v>
-      </c>
-      <c r="G212" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H212" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I212" t="str">
-        <v>-</v>
-      </c>
-      <c r="J212" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K212" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L212" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M212">
-        <v>200000</v>
-      </c>
-      <c r="N212" t="str">
-        <v>EQ-SAM-0021</v>
-      </c>
-      <c r="O212" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213">
-        <v>212</v>
-      </c>
-      <c r="B213" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C213" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="D213" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
-      </c>
-      <c r="E213" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F213">
-        <v>1</v>
-      </c>
-      <c r="G213" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H213" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I213" t="str">
-        <v>-</v>
-      </c>
-      <c r="J213" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K213" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L213" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M213">
-        <v>7000</v>
-      </c>
-      <c r="N213" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O213" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214">
-        <v>213</v>
-      </c>
-      <c r="B214" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C214" t="str">
-        <v>EQ-TRS-0002</v>
-      </c>
-      <c r="D214" t="str">
-        <v>1-B9701-FN17-65450010002/001-68</v>
-      </c>
-      <c r="E214" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F214">
-        <v>2</v>
-      </c>
-      <c r="G214" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H214" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I214" t="str">
-        <v>-</v>
-      </c>
-      <c r="J214" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K214" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L214" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M214">
-        <v>1000</v>
-      </c>
-      <c r="N214" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O214" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215">
-        <v>214</v>
-      </c>
-      <c r="B215" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C215" t="str">
-        <v>EQ-TRS-0003</v>
-      </c>
-      <c r="D215" t="str">
-        <v>1-B9701-FN17-65450010002/002-68</v>
-      </c>
-      <c r="E215" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F215">
-        <v>3</v>
-      </c>
-      <c r="G215" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H215" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I215" t="str">
-        <v>-</v>
-      </c>
-      <c r="J215" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K215" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L215" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M215">
-        <v>1000</v>
-      </c>
-      <c r="N215" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O215" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216">
-        <v>215</v>
-      </c>
-      <c r="B216" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C216" t="str">
-        <v>EQ-TRS-0004</v>
-      </c>
-      <c r="D216" t="str">
-        <v>1-B9701-FN17-65450010002/003-68</v>
-      </c>
-      <c r="E216" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F216">
-        <v>4</v>
-      </c>
-      <c r="G216" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H216" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I216" t="str">
-        <v>-</v>
-      </c>
-      <c r="J216" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K216" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L216" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M216">
-        <v>1000</v>
-      </c>
-      <c r="N216" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O216" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217">
-        <v>216</v>
-      </c>
-      <c r="B217" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C217" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="D217" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (43-1/2)</v>
-      </c>
-      <c r="E217" t="str">
-        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="F217">
-        <v>1</v>
-      </c>
-      <c r="G217" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H217" t="str">
-        <v>Patient Transfer Slide</v>
-      </c>
-      <c r="I217" t="str">
-        <v>-</v>
-      </c>
-      <c r="J217" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K217" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L217" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M217">
-        <v>8000</v>
-      </c>
-      <c r="N217" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="O217" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218">
-        <v>217</v>
-      </c>
-      <c r="B218" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C218" t="str">
-        <v>EQ-TRS-0006</v>
-      </c>
-      <c r="D218" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (43-2/2)</v>
-      </c>
-      <c r="E218" t="str">
-        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="F218">
-        <v>2</v>
-      </c>
-      <c r="G218" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H218" t="str">
-        <v>Patient Transfer Slide</v>
-      </c>
-      <c r="I218" t="str">
-        <v>-</v>
-      </c>
-      <c r="J218" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K218" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L218" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M218">
-        <v>8000</v>
-      </c>
-      <c r="N218" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="O218" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O218"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/ข้อมูลครุภัณฑ์/รายงานรายการครุภัณฑ์คงทนที่ยังไม่มีรูปภาพ.updated.xlsx
+++ b/ข้อมูลครุภัณฑ์/รายงานรายการครุภัณฑ์คงทนที่ยังไม่มีรูปภาพ.updated.xlsx
@@ -464,19 +464,19 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
         <v>6</v>
       </c>
       <c r="G3" t="str">
-        <v>0.0%</v>
+        <v>14.3%</v>
       </c>
     </row>
     <row r="4">
@@ -993,13 +993,13 @@
         <v>หุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C3" t="str">
-        <v>EQ-SIM-0001</v>
+        <v>EQ-SIM-0002</v>
       </c>
       <c r="D3" t="str">
         <v>Mini PC สำหรับควบคุมหุ่น (SIM MAN)</v>
@@ -1280,7 +1280,7 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C4" t="str">
-        <v>EQ-SIM-0003</v>
+        <v>EQ-SIM-0004</v>
       </c>
       <c r="D4" t="str">
         <v>จอ LED TOUCH Screen 32 นิ้ว (SIM MAN)</v>
@@ -1321,7 +1321,7 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C5" t="str">
-        <v>EQ-SIM-0005</v>
+        <v>EQ-SIM-0006</v>
       </c>
       <c r="D5" t="str">
         <v>เตียงหุ่น SIM MAN</v>
@@ -1362,7 +1362,7 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C6" t="str">
-        <v>EQ-SIM-0006</v>
+        <v>EQ-SIM-0007</v>
       </c>
       <c r="D6" t="str">
         <v>SIM MAN</v>
@@ -3247,7 +3247,7 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C3" t="str">
-        <v>EQ-SIM-0001</v>
+        <v>EQ-SIM-0002</v>
       </c>
       <c r="D3" t="str">
         <v>1-B9701-FA09-58450040001/001-68</v>
@@ -3280,7 +3280,7 @@
         <v>15000</v>
       </c>
       <c r="N3" t="str">
-        <v>EQ-SIM-0001</v>
+        <v>EQ-SIM-0002</v>
       </c>
       <c r="O3" t="str">
         <v/>
@@ -3294,7 +3294,7 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C4" t="str">
-        <v>EQ-SIM-0002</v>
+        <v>EQ-SIM-0003</v>
       </c>
       <c r="D4" t="str">
         <v>1-B9701-FA09-58450040001/002-68</v>
@@ -3327,7 +3327,7 @@
         <v>15000</v>
       </c>
       <c r="N4" t="str">
-        <v>EQ-SIM-0001</v>
+        <v>EQ-SIM-0002</v>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -3341,7 +3341,7 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C5" t="str">
-        <v>EQ-SIM-0003</v>
+        <v>EQ-SIM-0004</v>
       </c>
       <c r="D5" t="str">
         <v>1-B9701-FA09-66600010001/005-68</v>
@@ -3374,7 +3374,7 @@
         <v>80000</v>
       </c>
       <c r="N5" t="str">
-        <v>EQ-SIM-0003</v>
+        <v>EQ-SIM-0004</v>
       </c>
       <c r="O5" t="str">
         <v/>
@@ -3388,7 +3388,7 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C6" t="str">
-        <v>EQ-SIM-0004</v>
+        <v>EQ-SIM-0005</v>
       </c>
       <c r="D6" t="str">
         <v>1-B9701-FA09-66600010001/006-68</v>
@@ -3421,7 +3421,7 @@
         <v>80000</v>
       </c>
       <c r="N6" t="str">
-        <v>EQ-SIM-0003</v>
+        <v>EQ-SIM-0004</v>
       </c>
       <c r="O6" t="str">
         <v/>
@@ -3435,7 +3435,7 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C7" t="str">
-        <v>EQ-SIM-0005</v>
+        <v>EQ-SIM-0006</v>
       </c>
       <c r="D7" t="str">
         <v>1-B9701-FA17-65300010001/003-68</v>
@@ -3468,7 +3468,7 @@
         <v>50000</v>
       </c>
       <c r="N7" t="str">
-        <v>EQ-SIM-0005</v>
+        <v>EQ-SIM-0006</v>
       </c>
       <c r="O7" t="str">
         <v/>
@@ -3482,7 +3482,7 @@
         <v>(SIM MAN) อุปกรณ์จำลองสถานการณ์และหุ่นฝึกปฏิบัติการ</v>
       </c>
       <c r="C8" t="str">
-        <v>EQ-SIM-0006</v>
+        <v>EQ-SIM-0007</v>
       </c>
       <c r="D8" t="str">
         <v>1-B9701-FA17-65450010004/065-68</v>
@@ -3515,7 +3515,7 @@
         <v>4760000</v>
       </c>
       <c r="N8" t="str">
-        <v>EQ-SIM-0006</v>
+        <v>EQ-SIM-0007</v>
       </c>
       <c r="O8" t="str">
         <v/>

--- a/ข้อมูลครุภัณฑ์/รายงานรายการครุภัณฑ์คงทนที่ยังไม่มีรูปภาพ.updated.xlsx
+++ b/ข้อมูลครุภัณฑ์/รายงานรายการครุภัณฑ์คงทนที่ยังไม่มีรูปภาพ.updated.xlsx
@@ -1022,13 +1022,13 @@
         <v>21</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F27">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="G27" t="str">
-        <v>0.0%</v>
+        <v>47.6%</v>
       </c>
     </row>
     <row r="28">
@@ -1114,13 +1114,13 @@
         <v>373</v>
       </c>
       <c r="E31">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F31">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="G31" t="str">
-        <v>49.9%</v>
+        <v>52.5%</v>
       </c>
     </row>
   </sheetData>
@@ -1132,7 +1132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M47"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="32.83203125" customWidth="1"/>
@@ -2920,16 +2920,16 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C44" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="D44" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="E44" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="F44" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="G44">
         <v>10</v>
@@ -2941,7 +2941,7 @@
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J44" t="str">
-        <v>1-B9701-FA17-65450010004/055-68 ถึง 1-B9701-FA17-65450010004/064-68 (มี 10 เลข)</v>
+        <v>1-B9701-FA18-74400010005/001-68 ถึง 1-B9701-FA18-74400010005/010-68 (มี 10 เลข)</v>
       </c>
       <c r="K44" t="str">
         <v>ชั้น 3 อาคารวิทยบริการ</v>
@@ -2961,31 +2961,31 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C45" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-SAM-0021</v>
       </c>
       <c r="D45" t="str">
-        <v>SAM IPAD</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
       </c>
       <c r="E45" t="str">
-        <v>Apple</v>
+        <v>Cardionics</v>
       </c>
       <c r="F45" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="G45">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H45">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I45" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J45" t="str">
-        <v>1-B9701-FA18-74400010005/001-68 ถึง 1-B9701-FA18-74400010005/010-68 (มี 10 เลข)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (21-1/1)</v>
       </c>
       <c r="K45" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
+        <v>-</v>
       </c>
       <c r="L45" t="str">
         <v/>
@@ -2999,31 +2999,31 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C46" t="str">
-        <v>EQ-SAM-0021</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="D46" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="E46" t="str">
-        <v>Cardionics</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="F46" t="str">
-        <v>718-8804 SAM</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I46" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J46" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (21-1/1)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (42-1/1) ถึง 1-B9701-FN17-65450010002/003-68 (มี 4 เลข)</v>
       </c>
       <c r="K46" t="str">
         <v>-</v>
@@ -3043,90 +3043,49 @@
         <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C47" t="str">
-        <v>EQ-TRS-0001</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="D47" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
+        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="E47" t="str">
         <v>Upright Simulation</v>
       </c>
       <c r="F47" t="str">
-        <v>CPR Board (CPR-B)</v>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="G47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I47" t="str">
         <v>ยังไม่มีรูปภาพเลย (0%)</v>
       </c>
       <c r="J47" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (42-1/1) ถึง 1-B9701-FN17-65450010002/003-68 (มี 4 เลข)</v>
+        <v>2-B9701-FA17-65450010002/001-67 (43-1/2) ถึง 2-B9701-FA17-65450010002/001-67 (43-2/2) (มี 2 เลข)</v>
       </c>
       <c r="K47" t="str">
-        <v>-</v>
+        <v>ชั้น 3 อาคารวิทยบริการ</v>
       </c>
       <c r="L47" t="str">
         <v/>
       </c>
       <c r="M47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C48" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="D48" t="str">
-        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="E48" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="F48" t="str">
-        <v>Patient Transfer Slide</v>
-      </c>
-      <c r="G48">
-        <v>2</v>
-      </c>
-      <c r="H48">
-        <v>2</v>
-      </c>
-      <c r="I48" t="str">
-        <v>ยังไม่มีรูปภาพเลย (0%)</v>
-      </c>
-      <c r="J48" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (43-1/2) ถึง 2-B9701-FA17-65450010002/001-67 (43-2/2) (มี 2 เลข)</v>
-      </c>
-      <c r="K48" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="L48" t="str">
-        <v/>
-      </c>
-      <c r="M48" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M48"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M47"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O188"/>
+  <dimension ref="A1:O178"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -10720,22 +10679,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C162" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="D162" t="str">
-        <v>1-B9701-FA17-65450010004/055-68</v>
+        <v>1-B9701-FA18-74400010005/001-68</v>
       </c>
       <c r="E162" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F162">
         <v>1</v>
       </c>
       <c r="G162" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="H162" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I162" t="str">
         <v>-</v>
@@ -10750,10 +10709,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M162">
-        <v>735000</v>
+        <v>15000</v>
       </c>
       <c r="N162" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O162" t="str">
         <v/>
@@ -10767,22 +10726,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C163" t="str">
-        <v>EQ-SAM-0002</v>
+        <v>EQ-SAM-0012</v>
       </c>
       <c r="D163" t="str">
-        <v>1-B9701-FA17-65450010004/056-68</v>
+        <v>1-B9701-FA18-74400010005/002-68</v>
       </c>
       <c r="E163" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F163">
         <v>2</v>
       </c>
       <c r="G163" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="H163" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I163" t="str">
         <v>-</v>
@@ -10797,10 +10756,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M163">
-        <v>735000</v>
+        <v>15000</v>
       </c>
       <c r="N163" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O163" t="str">
         <v/>
@@ -10814,22 +10773,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C164" t="str">
-        <v>EQ-SAM-0003</v>
+        <v>EQ-SAM-0013</v>
       </c>
       <c r="D164" t="str">
-        <v>1-B9701-FA17-65450010004/057-68</v>
+        <v>1-B9701-FA18-74400010005/003-68</v>
       </c>
       <c r="E164" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F164">
         <v>3</v>
       </c>
       <c r="G164" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="H164" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I164" t="str">
         <v>-</v>
@@ -10844,10 +10803,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M164">
-        <v>735000</v>
+        <v>15000</v>
       </c>
       <c r="N164" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O164" t="str">
         <v/>
@@ -10861,22 +10820,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C165" t="str">
-        <v>EQ-SAM-0004</v>
+        <v>EQ-SAM-0014</v>
       </c>
       <c r="D165" t="str">
-        <v>1-B9701-FA17-65450010004/058-68</v>
+        <v>1-B9701-FA18-74400010005/004-68</v>
       </c>
       <c r="E165" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F165">
         <v>4</v>
       </c>
       <c r="G165" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="H165" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I165" t="str">
         <v>-</v>
@@ -10891,10 +10850,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M165">
-        <v>735000</v>
+        <v>15000</v>
       </c>
       <c r="N165" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O165" t="str">
         <v/>
@@ -10908,22 +10867,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C166" t="str">
-        <v>EQ-SAM-0005</v>
+        <v>EQ-SAM-0015</v>
       </c>
       <c r="D166" t="str">
-        <v>1-B9701-FA17-65450010004/059-68</v>
+        <v>1-B9701-FA18-74400010005/005-68</v>
       </c>
       <c r="E166" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F166">
         <v>5</v>
       </c>
       <c r="G166" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="H166" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I166" t="str">
         <v>-</v>
@@ -10938,10 +10897,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M166">
-        <v>735000</v>
+        <v>15000</v>
       </c>
       <c r="N166" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O166" t="str">
         <v/>
@@ -10955,22 +10914,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C167" t="str">
-        <v>EQ-SAM-0006</v>
+        <v>EQ-SAM-0016</v>
       </c>
       <c r="D167" t="str">
-        <v>1-B9701-FA17-65450010004/060-68</v>
+        <v>1-B9701-FA18-74400010005/006-68</v>
       </c>
       <c r="E167" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F167">
         <v>6</v>
       </c>
       <c r="G167" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="H167" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I167" t="str">
         <v>-</v>
@@ -10985,10 +10944,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M167">
-        <v>735000</v>
+        <v>15000</v>
       </c>
       <c r="N167" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O167" t="str">
         <v/>
@@ -11002,22 +10961,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C168" t="str">
-        <v>EQ-SAM-0007</v>
+        <v>EQ-SAM-0017</v>
       </c>
       <c r="D168" t="str">
-        <v>1-B9701-FA17-65450010004/061-68</v>
+        <v>1-B9701-FA18-74400010005/007-68</v>
       </c>
       <c r="E168" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F168">
         <v>7</v>
       </c>
       <c r="G168" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="H168" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I168" t="str">
         <v>-</v>
@@ -11032,10 +10991,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M168">
-        <v>735000</v>
+        <v>15000</v>
       </c>
       <c r="N168" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O168" t="str">
         <v/>
@@ -11049,22 +11008,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C169" t="str">
-        <v>EQ-SAM-0008</v>
+        <v>EQ-SAM-0018</v>
       </c>
       <c r="D169" t="str">
-        <v>1-B9701-FA17-65450010004/062-68</v>
+        <v>1-B9701-FA18-74400010005/008-68</v>
       </c>
       <c r="E169" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F169">
         <v>8</v>
       </c>
       <c r="G169" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="H169" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I169" t="str">
         <v>-</v>
@@ -11079,10 +11038,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M169">
-        <v>735000</v>
+        <v>15000</v>
       </c>
       <c r="N169" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O169" t="str">
         <v/>
@@ -11096,22 +11055,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C170" t="str">
-        <v>EQ-SAM-0009</v>
+        <v>EQ-SAM-0019</v>
       </c>
       <c r="D170" t="str">
-        <v>1-B9701-FA17-65450010004/063-68</v>
+        <v>1-B9701-FA18-74400010005/009-68</v>
       </c>
       <c r="E170" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F170">
         <v>9</v>
       </c>
       <c r="G170" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="H170" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I170" t="str">
         <v>-</v>
@@ -11126,10 +11085,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M170">
-        <v>735000</v>
+        <v>15000</v>
       </c>
       <c r="N170" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O170" t="str">
         <v/>
@@ -11143,22 +11102,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C171" t="str">
-        <v>EQ-SAM-0010</v>
+        <v>EQ-SAM-0020</v>
       </c>
       <c r="D171" t="str">
-        <v>1-B9701-FA17-65450010004/064-68</v>
+        <v>1-B9701-FA18-74400010005/010-68</v>
       </c>
       <c r="E171" t="str">
-        <v>SAM</v>
+        <v>SAM IPAD</v>
       </c>
       <c r="F171">
         <v>10</v>
       </c>
       <c r="G171" t="str">
-        <v>Cardionics</v>
+        <v>Apple</v>
       </c>
       <c r="H171" t="str">
-        <v>718-8804 SAM</v>
+        <v>iPad 10.2 Wi-Fi</v>
       </c>
       <c r="I171" t="str">
         <v>-</v>
@@ -11173,10 +11132,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M171">
-        <v>735000</v>
+        <v>15000</v>
       </c>
       <c r="N171" t="str">
-        <v>EQ-SAM-0001</v>
+        <v>EQ-SAM-0011</v>
       </c>
       <c r="O171" t="str">
         <v/>
@@ -11190,22 +11149,22 @@
         <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
       </c>
       <c r="C172" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-SAM-0021</v>
       </c>
       <c r="D172" t="str">
-        <v>1-B9701-FA18-74400010005/001-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (21-1/1)</v>
       </c>
       <c r="E172" t="str">
-        <v>SAM IPAD</v>
+        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
       </c>
       <c r="F172">
         <v>1</v>
       </c>
       <c r="G172" t="str">
-        <v>Apple</v>
+        <v>Cardionics</v>
       </c>
       <c r="H172" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
+        <v>718-8804 SAM</v>
       </c>
       <c r="I172" t="str">
         <v>-</v>
@@ -11220,10 +11179,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M172">
-        <v>15000</v>
+        <v>200000</v>
       </c>
       <c r="N172" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-SAM-0021</v>
       </c>
       <c r="O172" t="str">
         <v/>
@@ -11234,25 +11193,25 @@
         <v>172</v>
       </c>
       <c r="B173" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C173" t="str">
-        <v>EQ-SAM-0012</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="D173" t="str">
-        <v>1-B9701-FA18-74400010005/002-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
       </c>
       <c r="E173" t="str">
-        <v>SAM IPAD</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G173" t="str">
-        <v>Apple</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H173" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I173" t="str">
         <v>-</v>
@@ -11267,10 +11226,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M173">
-        <v>15000</v>
+        <v>7000</v>
       </c>
       <c r="N173" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O173" t="str">
         <v/>
@@ -11281,25 +11240,25 @@
         <v>173</v>
       </c>
       <c r="B174" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C174" t="str">
-        <v>EQ-SAM-0013</v>
+        <v>EQ-TRS-0002</v>
       </c>
       <c r="D174" t="str">
-        <v>1-B9701-FA18-74400010005/003-68</v>
+        <v>1-B9701-FN17-65450010002/001-68</v>
       </c>
       <c r="E174" t="str">
-        <v>SAM IPAD</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F174">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G174" t="str">
-        <v>Apple</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H174" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I174" t="str">
         <v>-</v>
@@ -11314,10 +11273,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M174">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="N174" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O174" t="str">
         <v/>
@@ -11328,25 +11287,25 @@
         <v>174</v>
       </c>
       <c r="B175" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C175" t="str">
-        <v>EQ-SAM-0014</v>
+        <v>EQ-TRS-0003</v>
       </c>
       <c r="D175" t="str">
-        <v>1-B9701-FA18-74400010005/004-68</v>
+        <v>1-B9701-FN17-65450010002/002-68</v>
       </c>
       <c r="E175" t="str">
-        <v>SAM IPAD</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F175">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G175" t="str">
-        <v>Apple</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H175" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I175" t="str">
         <v>-</v>
@@ -11361,10 +11320,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M175">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="N175" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O175" t="str">
         <v/>
@@ -11375,25 +11334,25 @@
         <v>175</v>
       </c>
       <c r="B176" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C176" t="str">
-        <v>EQ-SAM-0015</v>
+        <v>EQ-TRS-0004</v>
       </c>
       <c r="D176" t="str">
-        <v>1-B9701-FA18-74400010005/005-68</v>
+        <v>1-B9701-FN17-65450010002/003-68</v>
       </c>
       <c r="E176" t="str">
-        <v>SAM IPAD</v>
+        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
       </c>
       <c r="F176">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G176" t="str">
-        <v>Apple</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H176" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
+        <v>CPR Board (CPR-B)</v>
       </c>
       <c r="I176" t="str">
         <v>-</v>
@@ -11408,10 +11367,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M176">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="N176" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-TRS-0001</v>
       </c>
       <c r="O176" t="str">
         <v/>
@@ -11422,25 +11381,25 @@
         <v>176</v>
       </c>
       <c r="B177" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C177" t="str">
-        <v>EQ-SAM-0016</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="D177" t="str">
-        <v>1-B9701-FA18-74400010005/006-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (43-1/2)</v>
       </c>
       <c r="E177" t="str">
-        <v>SAM IPAD</v>
+        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="F177">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G177" t="str">
-        <v>Apple</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H177" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="I177" t="str">
         <v>-</v>
@@ -11455,10 +11414,10 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M177">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="N177" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="O177" t="str">
         <v/>
@@ -11469,25 +11428,25 @@
         <v>177</v>
       </c>
       <c r="B178" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
+        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="C178" t="str">
-        <v>EQ-SAM-0017</v>
+        <v>EQ-TRS-0006</v>
       </c>
       <c r="D178" t="str">
-        <v>1-B9701-FA18-74400010005/007-68</v>
+        <v>2-B9701-FA17-65450010002/001-67 (43-2/2)</v>
       </c>
       <c r="E178" t="str">
-        <v>SAM IPAD</v>
+        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
       </c>
       <c r="F178">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G178" t="str">
-        <v>Apple</v>
+        <v>Upright Simulation</v>
       </c>
       <c r="H178" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
+        <v>Patient Transfer Slide</v>
       </c>
       <c r="I178" t="str">
         <v>-</v>
@@ -11502,488 +11461,18 @@
         <v>สมบูรณ์ดี</v>
       </c>
       <c r="M178">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="N178" t="str">
-        <v>EQ-SAM-0011</v>
+        <v>EQ-TRS-0005</v>
       </c>
       <c r="O178" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179">
-        <v>178</v>
-      </c>
-      <c r="B179" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C179" t="str">
-        <v>EQ-SAM-0018</v>
-      </c>
-      <c r="D179" t="str">
-        <v>1-B9701-FA18-74400010005/008-68</v>
-      </c>
-      <c r="E179" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F179">
-        <v>8</v>
-      </c>
-      <c r="G179" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H179" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I179" t="str">
-        <v>-</v>
-      </c>
-      <c r="J179" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K179" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L179" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M179">
-        <v>15000</v>
-      </c>
-      <c r="N179" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O179" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180">
-        <v>179</v>
-      </c>
-      <c r="B180" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C180" t="str">
-        <v>EQ-SAM-0019</v>
-      </c>
-      <c r="D180" t="str">
-        <v>1-B9701-FA18-74400010005/009-68</v>
-      </c>
-      <c r="E180" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F180">
-        <v>9</v>
-      </c>
-      <c r="G180" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H180" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I180" t="str">
-        <v>-</v>
-      </c>
-      <c r="J180" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K180" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L180" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M180">
-        <v>15000</v>
-      </c>
-      <c r="N180" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O180" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181">
-        <v>180</v>
-      </c>
-      <c r="B181" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C181" t="str">
-        <v>EQ-SAM-0020</v>
-      </c>
-      <c r="D181" t="str">
-        <v>1-B9701-FA18-74400010005/010-68</v>
-      </c>
-      <c r="E181" t="str">
-        <v>SAM IPAD</v>
-      </c>
-      <c r="F181">
-        <v>10</v>
-      </c>
-      <c r="G181" t="str">
-        <v>Apple</v>
-      </c>
-      <c r="H181" t="str">
-        <v>iPad 10.2 Wi-Fi</v>
-      </c>
-      <c r="I181" t="str">
-        <v>-</v>
-      </c>
-      <c r="J181" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K181" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L181" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M181">
-        <v>15000</v>
-      </c>
-      <c r="N181" t="str">
-        <v>EQ-SAM-0011</v>
-      </c>
-      <c r="O181" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182">
-        <v>181</v>
-      </c>
-      <c r="B182" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกาย และอุปกรณ์</v>
-      </c>
-      <c r="C182" t="str">
-        <v>EQ-SAM-0021</v>
-      </c>
-      <c r="D182" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (21-1/1)</v>
-      </c>
-      <c r="E182" t="str">
-        <v>หุ่นฝึกฟังเสียงในร่างกายผู้ใหญ่</v>
-      </c>
-      <c r="F182">
-        <v>1</v>
-      </c>
-      <c r="G182" t="str">
-        <v>Cardionics</v>
-      </c>
-      <c r="H182" t="str">
-        <v>718-8804 SAM</v>
-      </c>
-      <c r="I182" t="str">
-        <v>-</v>
-      </c>
-      <c r="J182" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K182" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L182" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M182">
-        <v>200000</v>
-      </c>
-      <c r="N182" t="str">
-        <v>EQ-SAM-0021</v>
-      </c>
-      <c r="O182" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183">
-        <v>182</v>
-      </c>
-      <c r="B183" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C183" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="D183" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (42-1/1)</v>
-      </c>
-      <c r="E183" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F183">
-        <v>1</v>
-      </c>
-      <c r="G183" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H183" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I183" t="str">
-        <v>-</v>
-      </c>
-      <c r="J183" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K183" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L183" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M183">
-        <v>7000</v>
-      </c>
-      <c r="N183" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O183" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184">
-        <v>183</v>
-      </c>
-      <c r="B184" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C184" t="str">
-        <v>EQ-TRS-0002</v>
-      </c>
-      <c r="D184" t="str">
-        <v>1-B9701-FN17-65450010002/001-68</v>
-      </c>
-      <c r="E184" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F184">
-        <v>2</v>
-      </c>
-      <c r="G184" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H184" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I184" t="str">
-        <v>-</v>
-      </c>
-      <c r="J184" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K184" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L184" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M184">
-        <v>1000</v>
-      </c>
-      <c r="N184" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O184" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185">
-        <v>184</v>
-      </c>
-      <c r="B185" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C185" t="str">
-        <v>EQ-TRS-0003</v>
-      </c>
-      <c r="D185" t="str">
-        <v>1-B9701-FN17-65450010002/002-68</v>
-      </c>
-      <c r="E185" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F185">
-        <v>3</v>
-      </c>
-      <c r="G185" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H185" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I185" t="str">
-        <v>-</v>
-      </c>
-      <c r="J185" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K185" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L185" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M185">
-        <v>1000</v>
-      </c>
-      <c r="N185" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O185" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186">
-        <v>185</v>
-      </c>
-      <c r="B186" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C186" t="str">
-        <v>EQ-TRS-0004</v>
-      </c>
-      <c r="D186" t="str">
-        <v>1-B9701-FN17-65450010002/003-68</v>
-      </c>
-      <c r="E186" t="str">
-        <v>กระดานรองหลังผู้ป่วยสำหรับ CPR</v>
-      </c>
-      <c r="F186">
-        <v>4</v>
-      </c>
-      <c r="G186" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H186" t="str">
-        <v>CPR Board (CPR-B)</v>
-      </c>
-      <c r="I186" t="str">
-        <v>-</v>
-      </c>
-      <c r="J186" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K186" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L186" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M186">
-        <v>1000</v>
-      </c>
-      <c r="N186" t="str">
-        <v>EQ-TRS-0001</v>
-      </c>
-      <c r="O186" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187">
-        <v>186</v>
-      </c>
-      <c r="B187" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C187" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="D187" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (43-1/2)</v>
-      </c>
-      <c r="E187" t="str">
-        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="F187">
-        <v>1</v>
-      </c>
-      <c r="G187" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H187" t="str">
-        <v>Patient Transfer Slide</v>
-      </c>
-      <c r="I187" t="str">
-        <v>-</v>
-      </c>
-      <c r="J187" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K187" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L187" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M187">
-        <v>8000</v>
-      </c>
-      <c r="N187" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="O187" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188">
-        <v>187</v>
-      </c>
-      <c r="B188" t="str">
-        <v>อุปกรณ์เคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="C188" t="str">
-        <v>EQ-TRS-0006</v>
-      </c>
-      <c r="D188" t="str">
-        <v>2-B9701-FA17-65450010002/001-67 (43-2/2)</v>
-      </c>
-      <c r="E188" t="str">
-        <v>Slide สำหรับเคลื่อนย้ายผู้ป่วย</v>
-      </c>
-      <c r="F188">
-        <v>2</v>
-      </c>
-      <c r="G188" t="str">
-        <v>Upright Simulation</v>
-      </c>
-      <c r="H188" t="str">
-        <v>Patient Transfer Slide</v>
-      </c>
-      <c r="I188" t="str">
-        <v>-</v>
-      </c>
-      <c r="J188" t="str">
-        <v>ชั้น 3 อาคารวิทยบริการ</v>
-      </c>
-      <c r="K188" t="str">
-        <v>พร้อมใช้งาน</v>
-      </c>
-      <c r="L188" t="str">
-        <v>สมบูรณ์ดี</v>
-      </c>
-      <c r="M188">
-        <v>8000</v>
-      </c>
-      <c r="N188" t="str">
-        <v>EQ-TRS-0005</v>
-      </c>
-      <c r="O188" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O178"/>
   </ignoredErrors>
 </worksheet>
 </file>